--- a/audit/docker_benchmark_reports/192.168.1.8_section6.xlsx
+++ b/audit/docker_benchmark_reports/192.168.1.8_section6.xlsx
@@ -846,7 +846,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-21T18:45:56Z</t>
+          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-28T13:05:33Z</t>
         </is>
       </c>
     </row>
